--- a/data/vrv-schedule-template.xlsx
+++ b/data/vrv-schedule-template.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\Test 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B4C447-EE61-4216-B6FE-7A5B725ABD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB8F79F-E923-47A9-B9D5-AAFFE9AA3E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4968" yWindow="2892" windowWidth="17160" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VRV Schedule" sheetId="3" r:id="rId1"/>
-    <sheet name="Indoor Data" sheetId="4" state="hidden" r:id="rId2"/>
-    <sheet name="Outdoor Data" sheetId="5" state="hidden" r:id="rId3"/>
+    <sheet name="Indoor Data" sheetId="4" r:id="rId2"/>
+    <sheet name="Outdoor Data" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="228">
   <si>
     <t>Name</t>
   </si>
@@ -611,145 +611,124 @@
     <t>hp</t>
   </si>
   <si>
-    <t>GF-01</t>
-  </si>
-  <si>
-    <t>BEDROOM 01</t>
-  </si>
-  <si>
-    <t>GF-02</t>
-  </si>
-  <si>
-    <t>BEDROOM 02</t>
-  </si>
-  <si>
-    <t>GF-03</t>
-  </si>
-  <si>
-    <t>BEDROOM 03</t>
-  </si>
-  <si>
-    <t>GF-04</t>
-  </si>
-  <si>
-    <t>BEDROOM 04</t>
-  </si>
-  <si>
-    <t>GF-05</t>
-  </si>
-  <si>
-    <t>BEDROOM 05</t>
-  </si>
-  <si>
-    <t>GF-06</t>
-  </si>
-  <si>
-    <t>MAIDS ROOM</t>
-  </si>
-  <si>
-    <t>GF-07</t>
-  </si>
-  <si>
-    <t>KITCHEN</t>
-  </si>
-  <si>
-    <t>GF-08</t>
-  </si>
-  <si>
-    <t>STORE 1,2 / LIFT LOBBY 01</t>
-  </si>
-  <si>
-    <t>GF-10</t>
-  </si>
-  <si>
-    <t>CORRIDOR / LIFT LOBBY 02</t>
-  </si>
-  <si>
-    <t>RXQ18ANRYFK</t>
+    <t>FCU-BF-01</t>
+  </si>
+  <si>
+    <t>BASEMENT FLOOR</t>
+  </si>
+  <si>
+    <t>FCU-BF-02</t>
+  </si>
+  <si>
+    <t>FCU-BF-03</t>
+  </si>
+  <si>
+    <t>FCU-BF-04</t>
+  </si>
+  <si>
+    <t>FCU-BF-05</t>
+  </si>
+  <si>
+    <t>FCU-BF-06</t>
+  </si>
+  <si>
+    <t>FCU-BF-07</t>
+  </si>
+  <si>
+    <t>FCU-BF-08</t>
+  </si>
+  <si>
+    <t>FCU-BF-09</t>
+  </si>
+  <si>
+    <t>FCU-BF-10</t>
+  </si>
+  <si>
+    <t>FCU-BF-11</t>
+  </si>
+  <si>
+    <t>FCU-BF-12</t>
+  </si>
+  <si>
+    <t>FCU-BF-13</t>
+  </si>
+  <si>
+    <t>FCU-GF-01</t>
+  </si>
+  <si>
+    <t>GROUND FLOOR</t>
+  </si>
+  <si>
+    <t>FCU-GF-02</t>
+  </si>
+  <si>
+    <t>FCU-GF-03</t>
+  </si>
+  <si>
+    <t>FCU-GF-04</t>
+  </si>
+  <si>
+    <t>FCU-GF-05</t>
+  </si>
+  <si>
+    <t>FCU-GF-06</t>
+  </si>
+  <si>
+    <t>FCU-FF-01</t>
+  </si>
+  <si>
+    <t>FIRST FLOOR</t>
+  </si>
+  <si>
+    <t>FCU-FF-02</t>
+  </si>
+  <si>
+    <t>FCU-FF-03</t>
+  </si>
+  <si>
+    <t>FCU-FF-04</t>
+  </si>
+  <si>
+    <t>FCU-FF-05</t>
+  </si>
+  <si>
+    <t>FCU-FF-06</t>
+  </si>
+  <si>
+    <t>FCU-FF-07</t>
+  </si>
+  <si>
+    <t>FCU-RF-01</t>
+  </si>
+  <si>
+    <t>ROOF FLOOR</t>
+  </si>
+  <si>
+    <t>FCU-RF-02</t>
+  </si>
+  <si>
+    <t>RXYTQ36U5YF</t>
+  </si>
+  <si>
+    <t>VRV-BF</t>
+  </si>
+  <si>
+    <t>RXYTQ24U5YF</t>
   </si>
   <si>
     <t>VRV-GF</t>
   </si>
   <si>
+    <t>RXYTQ30U5YF</t>
+  </si>
+  <si>
     <t>VRV-FF</t>
   </si>
   <si>
-    <t>RXQ20ANRYFK</t>
-  </si>
-  <si>
-    <t>FF-01</t>
-  </si>
-  <si>
-    <t>KIDS ROOM</t>
-  </si>
-  <si>
-    <t>FF-02</t>
-  </si>
-  <si>
-    <t>SHOW KITCHEN / DINING</t>
-  </si>
-  <si>
-    <t>FF-03</t>
-  </si>
-  <si>
-    <t>SITTING AREA A</t>
-  </si>
-  <si>
-    <t>FF-04</t>
-  </si>
-  <si>
-    <t>SITTING AREA B</t>
-  </si>
-  <si>
-    <t>FF-05</t>
-  </si>
-  <si>
-    <t>MASSAGE / SALOON</t>
-  </si>
-  <si>
-    <t>FF-06</t>
-  </si>
-  <si>
-    <t>LOBBY / LINEN AREA</t>
-  </si>
-  <si>
-    <t>VRV-SF</t>
-  </si>
-  <si>
-    <t>SF-01</t>
-  </si>
-  <si>
-    <t>MASTER BEDROOM</t>
-  </si>
-  <si>
-    <t>SF-02</t>
-  </si>
-  <si>
-    <t>MASTER DRESS</t>
-  </si>
-  <si>
-    <t>SF-03</t>
-  </si>
-  <si>
-    <t>MASTEROFFICE / PANTRY</t>
-  </si>
-  <si>
-    <t>SF-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GYM </t>
-  </si>
-  <si>
-    <t>SF-05</t>
-  </si>
-  <si>
-    <t>DRESSING ROOM</t>
+    <t>{Customer}</t>
   </si>
   <si>
     <t>{Project_Name}</t>
-  </si>
-  <si>
-    <t>{Customer_Name}</t>
   </si>
 </sst>
 </file>
@@ -1765,12 +1744,75 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1795,9 +1837,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1813,68 +1852,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1917,7 +1896,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>533475</xdr:colOff>
+      <xdr:colOff>596975</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>57171</xdr:rowOff>
     </xdr:to>
@@ -2305,7 +2284,7 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.77734375" style="1"/>
-    <col min="2" max="2" width="15.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="33" style="1" customWidth="1"/>
     <col min="5" max="5" width="7.77734375" style="1" customWidth="1"/>
@@ -2349,7 +2328,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="2:38" x14ac:dyDescent="0.25">
@@ -2357,95 +2336,95 @@
         <v>51</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:38" ht="18.899999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="89"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="89"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="89"/>
-      <c r="H6" s="89"/>
-      <c r="I6" s="89"/>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="89"/>
-      <c r="M6" s="89"/>
-      <c r="N6" s="89"/>
-      <c r="O6" s="89"/>
-      <c r="P6" s="89"/>
-      <c r="Q6" s="89"/>
-      <c r="R6" s="89"/>
-      <c r="S6" s="89"/>
-      <c r="T6" s="89"/>
-      <c r="U6" s="89"/>
-      <c r="V6" s="89"/>
-      <c r="W6" s="89"/>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="89"/>
-      <c r="AA6" s="89"/>
-      <c r="AB6" s="89"/>
-      <c r="AC6" s="89"/>
-      <c r="AD6" s="89"/>
-      <c r="AE6" s="89"/>
-      <c r="AF6" s="89"/>
-      <c r="AG6" s="89"/>
-      <c r="AH6" s="89"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
+      <c r="S6" s="110"/>
+      <c r="T6" s="110"/>
+      <c r="U6" s="110"/>
+      <c r="V6" s="110"/>
+      <c r="W6" s="110"/>
+      <c r="X6" s="110"/>
+      <c r="Y6" s="110"/>
+      <c r="Z6" s="110"/>
+      <c r="AA6" s="110"/>
+      <c r="AB6" s="110"/>
+      <c r="AC6" s="110"/>
+      <c r="AD6" s="110"/>
+      <c r="AE6" s="110"/>
+      <c r="AF6" s="110"/>
+      <c r="AG6" s="110"/>
+      <c r="AH6" s="110"/>
     </row>
     <row r="7" spans="2:38" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="113"/>
-      <c r="H7" s="90" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="111" t="s">
         <v>175</v>
       </c>
-      <c r="I7" s="91"/>
-      <c r="J7" s="91"/>
-      <c r="K7" s="91"/>
-      <c r="L7" s="91"/>
-      <c r="M7" s="91"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="91"/>
-      <c r="P7" s="91"/>
-      <c r="Q7" s="91"/>
-      <c r="R7" s="91"/>
-      <c r="S7" s="91"/>
-      <c r="T7" s="91"/>
-      <c r="U7" s="92"/>
-      <c r="V7" s="90" t="s">
+      <c r="I7" s="112"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="112"/>
+      <c r="T7" s="112"/>
+      <c r="U7" s="113"/>
+      <c r="V7" s="111" t="s">
         <v>176</v>
       </c>
-      <c r="W7" s="91"/>
-      <c r="X7" s="91"/>
-      <c r="Y7" s="91"/>
-      <c r="Z7" s="91"/>
-      <c r="AA7" s="91"/>
-      <c r="AB7" s="91"/>
-      <c r="AC7" s="91"/>
-      <c r="AD7" s="91"/>
-      <c r="AE7" s="91"/>
-      <c r="AF7" s="91"/>
-      <c r="AG7" s="91"/>
-      <c r="AH7" s="92"/>
+      <c r="W7" s="112"/>
+      <c r="X7" s="112"/>
+      <c r="Y7" s="112"/>
+      <c r="Z7" s="112"/>
+      <c r="AA7" s="112"/>
+      <c r="AB7" s="112"/>
+      <c r="AC7" s="112"/>
+      <c r="AD7" s="112"/>
+      <c r="AE7" s="112"/>
+      <c r="AF7" s="112"/>
+      <c r="AG7" s="112"/>
+      <c r="AH7" s="113"/>
     </row>
     <row r="8" spans="2:38" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="114" t="s">
+      <c r="D8" s="94" t="s">
         <v>1</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -2457,16 +2436,16 @@
       <c r="G8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="87" t="s">
+      <c r="I8" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="95" t="s">
+      <c r="J8" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="95" t="s">
+      <c r="K8" s="102" t="s">
         <v>5</v>
       </c>
       <c r="L8" s="19" t="s">
@@ -2487,7 +2466,7 @@
       <c r="Q8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="R8" s="95" t="s">
+      <c r="R8" s="102" t="s">
         <v>10</v>
       </c>
       <c r="S8" s="19" t="s">
@@ -2499,26 +2478,26 @@
       <c r="U8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="V8" s="93" t="s">
+      <c r="V8" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="W8" s="95" t="s">
+      <c r="W8" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="X8" s="87" t="s">
+      <c r="X8" s="108" t="s">
         <v>177</v>
       </c>
-      <c r="Y8" s="98" t="s">
+      <c r="Y8" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="99"/>
-      <c r="AA8" s="97" t="s">
+      <c r="Z8" s="119"/>
+      <c r="AA8" s="117" t="s">
         <v>49</v>
       </c>
-      <c r="AB8" s="95" t="s">
+      <c r="AB8" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="AC8" s="95" t="s">
+      <c r="AC8" s="102" t="s">
         <v>10</v>
       </c>
       <c r="AD8" s="19" t="s">
@@ -2538,124 +2517,124 @@
       </c>
     </row>
     <row r="9" spans="2:38" ht="28.8" x14ac:dyDescent="0.25">
-      <c r="B9" s="117"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="107" t="s">
+      <c r="B9" s="98"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="107" t="s">
+      <c r="F9" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="109" t="s">
+      <c r="G9" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="94"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="95"/>
-      <c r="K9" s="95"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="102"/>
+      <c r="K9" s="102"/>
       <c r="L9" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="85" t="s">
+      <c r="M9" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="85" t="s">
+      <c r="N9" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="O9" s="85" t="s">
+      <c r="O9" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="P9" s="85" t="s">
+      <c r="P9" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="Q9" s="85" t="s">
+      <c r="Q9" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="95"/>
-      <c r="S9" s="85" t="s">
+      <c r="R9" s="102"/>
+      <c r="S9" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="85" t="s">
+      <c r="T9" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="101" t="s">
+      <c r="U9" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="V9" s="93"/>
-      <c r="W9" s="95"/>
-      <c r="X9" s="87"/>
+      <c r="V9" s="114"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="108"/>
       <c r="Y9" s="22" t="s">
         <v>174</v>
       </c>
       <c r="Z9" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="AA9" s="95"/>
-      <c r="AB9" s="100"/>
-      <c r="AC9" s="95"/>
-      <c r="AD9" s="85" t="s">
+      <c r="AA9" s="102"/>
+      <c r="AB9" s="120"/>
+      <c r="AC9" s="102"/>
+      <c r="AD9" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="AE9" s="85" t="s">
+      <c r="AE9" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="AF9" s="85" t="s">
+      <c r="AF9" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="AG9" s="85" t="s">
+      <c r="AG9" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="AH9" s="101" t="s">
+      <c r="AH9" s="103" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="118"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="108"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="87"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="107"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="102"/>
+      <c r="K10" s="102"/>
       <c r="L10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="95"/>
-      <c r="N10" s="95"/>
-      <c r="O10" s="95"/>
-      <c r="P10" s="95"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="95"/>
-      <c r="S10" s="95"/>
-      <c r="T10" s="95"/>
-      <c r="U10" s="106"/>
-      <c r="V10" s="96"/>
-      <c r="W10" s="86"/>
-      <c r="X10" s="88"/>
+      <c r="M10" s="102"/>
+      <c r="N10" s="102"/>
+      <c r="O10" s="102"/>
+      <c r="P10" s="102"/>
+      <c r="Q10" s="102"/>
+      <c r="R10" s="102"/>
+      <c r="S10" s="102"/>
+      <c r="T10" s="102"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="116"/>
+      <c r="W10" s="101"/>
+      <c r="X10" s="109"/>
       <c r="Y10" s="23" t="s">
         <v>21</v>
       </c>
       <c r="Z10" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="AA10" s="86"/>
+      <c r="AA10" s="101"/>
       <c r="AB10" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="AC10" s="86"/>
-      <c r="AD10" s="86"/>
-      <c r="AE10" s="86"/>
-      <c r="AF10" s="86"/>
-      <c r="AG10" s="86"/>
-      <c r="AH10" s="102"/>
+      <c r="AC10" s="101"/>
+      <c r="AD10" s="101"/>
+      <c r="AE10" s="101"/>
+      <c r="AF10" s="101"/>
+      <c r="AG10" s="101"/>
+      <c r="AH10" s="121"/>
     </row>
     <row r="11" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B11" s="103" t="s">
-        <v>207</v>
+      <c r="B11" s="85" t="s">
+        <v>221</v>
       </c>
       <c r="C11" s="57" t="s">
         <v>188</v>
@@ -2664,24 +2643,24 @@
         <v>189</v>
       </c>
       <c r="E11" s="16">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="F11" s="16">
-        <v>3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G11" s="17">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="I11" s="60">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="J11" s="61" t="str">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K11" s="61" t="str">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -2693,39 +2672,39 @@
       </c>
       <c r="M11" s="61">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="N11" s="61">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="O11" s="62">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>266.67</v>
+        <v>350</v>
       </c>
       <c r="P11" s="63">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.151</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q11" s="61" t="str">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>35 - 39</v>
+        <v>27 - 33</v>
       </c>
       <c r="R11" s="61" t="str">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S11" s="61">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="T11" s="61" t="str">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>700 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U11" s="64">
         <f>IF($H11="","",VLOOKUP($H11,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>27</v>
+        <v>35.5</v>
       </c>
       <c r="V11" s="65"/>
       <c r="W11" s="66"/>
@@ -2742,32 +2721,32 @@
       <c r="AH11" s="11"/>
     </row>
     <row r="12" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B12" s="104"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="58" t="s">
         <v>190</v>
       </c>
       <c r="D12" s="58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E12" s="13">
-        <v>4.0999999999999996</v>
+        <v>7.1</v>
       </c>
       <c r="F12" s="13">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="G12" s="18">
-        <v>207</v>
+        <v>350</v>
       </c>
       <c r="H12" s="68" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I12" s="69">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J12" s="70" t="str">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K12" s="70" t="str">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -2779,39 +2758,39 @@
       </c>
       <c r="M12" s="70">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>7.9</v>
       </c>
       <c r="N12" s="70">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="O12" s="71">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>383.33</v>
       </c>
       <c r="P12" s="72">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q12" s="70" t="str">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>29 - 35</v>
       </c>
       <c r="R12" s="70" t="str">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S12" s="70">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="T12" s="70" t="str">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U12" s="73">
         <f>IF($H12="","",VLOOKUP($H12,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="V12" s="74"/>
       <c r="W12" s="75"/>
@@ -2861,32 +2840,32 @@
       </c>
     </row>
     <row r="13" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B13" s="104"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="58" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E13" s="13">
-        <v>4.0999999999999996</v>
+        <v>9</v>
       </c>
       <c r="F13" s="13">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="G13" s="18">
-        <v>210</v>
+        <v>812</v>
       </c>
       <c r="H13" s="68" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I13" s="69">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J13" s="70" t="str">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K13" s="70" t="str">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -2898,56 +2877,56 @@
       </c>
       <c r="M13" s="70">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>9.9</v>
       </c>
       <c r="N13" s="70">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="O13" s="71">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P13" s="72">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q13" s="70" t="str">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>31 - 36</v>
       </c>
       <c r="R13" s="70" t="str">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S13" s="70">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="T13" s="70" t="str">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U13" s="73">
         <f>IF($H13="","",VLOOKUP($H13,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="V13" s="74" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="W13" s="75" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="X13" s="76"/>
       <c r="Y13" s="75">
         <v>46</v>
       </c>
       <c r="Z13" s="75">
-        <v>40.4</v>
+        <v>77.7</v>
       </c>
       <c r="AA13" s="77">
         <f>IF(W14="","",I26/X26)</f>
-        <v>1.0733333333333333</v>
+        <v>0.93444444444444441</v>
       </c>
       <c r="AB13" s="75"/>
       <c r="AC13" s="5"/>
@@ -2965,32 +2944,32 @@
       <c r="AL13" s="52"/>
     </row>
     <row r="14" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B14" s="104"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="58" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D14" s="58" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E14" s="13">
-        <v>4.0999999999999996</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F14" s="13">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="G14" s="18">
-        <v>210</v>
+        <v>318</v>
       </c>
       <c r="H14" s="68" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I14" s="69">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J14" s="70" t="str">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K14" s="70" t="str">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3002,45 +2981,45 @@
       </c>
       <c r="M14" s="70">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>2.5</v>
       </c>
       <c r="N14" s="70">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="O14" s="71">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="P14" s="72">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q14" s="70" t="str">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>25 - 30</v>
       </c>
       <c r="R14" s="70" t="str">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S14" s="70">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="T14" s="70" t="str">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U14" s="73">
         <f>IF($H14="","",VLOOKUP($H14,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>23.5</v>
       </c>
       <c r="V14" s="74" t="s">
         <v>23</v>
       </c>
       <c r="W14" s="75" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="X14" s="76">
         <f>IF($W14="",0,VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
@@ -3051,7 +3030,7 @@
       <c r="AA14" s="75"/>
       <c r="AB14" s="75">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>10.4</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AC14" s="5" t="str">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -3059,62 +3038,62 @@
       </c>
       <c r="AD14" s="5">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>26.9</v>
-      </c>
-      <c r="AE14" s="5" t="str">
+        <v>24</v>
+      </c>
+      <c r="AE14" s="5">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF14" s="5" t="str">
+        <v>32</v>
+      </c>
+      <c r="AF14" s="5">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>12.7</v>
       </c>
       <c r="AG14" s="5" t="str">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>1,240 x 1,657 x 765</v>
+        <v>1,240 x 1,685 x 765</v>
       </c>
       <c r="AH14" s="48">
         <f>IF($W14="","",VLOOKUP($W14,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="AJ14" s="52" t="s">
         <v>186</v>
       </c>
       <c r="AK14" s="54">
         <f>(I26/AK13)/25</f>
-        <v>17.563636363636363</v>
+        <v>30.581818181818178</v>
       </c>
       <c r="AL14" s="52" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="15" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B15" s="104"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="58" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D15" s="58" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E15" s="13">
-        <v>4.3</v>
+        <v>7.1</v>
       </c>
       <c r="F15" s="13">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="G15" s="18">
-        <v>227</v>
+        <v>350</v>
       </c>
       <c r="H15" s="68" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="I15" s="69">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J15" s="70" t="str">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K15" s="70" t="str">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3126,56 +3105,56 @@
       </c>
       <c r="M15" s="70">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>7.9</v>
       </c>
       <c r="N15" s="70">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="O15" s="71">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>383.33</v>
       </c>
       <c r="P15" s="72">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q15" s="70" t="str">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>29 - 35</v>
       </c>
       <c r="R15" s="70" t="str">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S15" s="70">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="T15" s="70" t="str">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U15" s="73">
         <f>IF($H15="","",VLOOKUP($H15,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="V15" s="74" t="s">
         <v>41</v>
       </c>
       <c r="W15" s="75" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="X15" s="76">
         <f>IF($W15="",0,VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="Y15" s="75"/>
       <c r="Z15" s="75"/>
       <c r="AA15" s="75"/>
       <c r="AB15" s="75">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AC15" s="5" t="str">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -3183,52 +3162,52 @@
       </c>
       <c r="AD15" s="5">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="AE15" s="5" t="str">
+        <v>24</v>
+      </c>
+      <c r="AE15" s="5">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF15" s="5" t="str">
+        <v>32</v>
+      </c>
+      <c r="AF15" s="5">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>12.7</v>
       </c>
       <c r="AG15" s="5" t="str">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>930 x 1,657 x 765</v>
+        <v>1,240 x 1,685 x 765</v>
       </c>
       <c r="AH15" s="48">
         <f>IF($W15="","",VLOOKUP($W15,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>165</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B16" s="104"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="58" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D16" s="58" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="E16" s="13">
-        <v>2.9</v>
+        <v>7.1</v>
       </c>
       <c r="F16" s="13">
-        <v>2.2000000000000002</v>
+        <v>5.2</v>
       </c>
       <c r="G16" s="18">
-        <v>138</v>
+        <v>350</v>
       </c>
       <c r="H16" s="68" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="I16" s="69">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J16" s="70" t="str">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K16" s="70" t="str">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3240,105 +3219,109 @@
       </c>
       <c r="M16" s="70">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4</v>
+        <v>7.9</v>
       </c>
       <c r="N16" s="70">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="O16" s="71">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>266.67</v>
+        <v>383.33</v>
       </c>
       <c r="P16" s="72">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.151</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q16" s="70" t="str">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>35 - 39</v>
+        <v>29 - 35</v>
       </c>
       <c r="R16" s="70" t="str">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S16" s="70">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="T16" s="70" t="str">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>700 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U16" s="73">
         <f>IF($H16="","",VLOOKUP($H16,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>27</v>
-      </c>
-      <c r="V16" s="74"/>
-      <c r="W16" s="75"/>
+        <v>36.5</v>
+      </c>
+      <c r="V16" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="W16" s="75" t="s">
+        <v>171</v>
+      </c>
       <c r="X16" s="76">
         <f>IF($W16="",0,VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Y16" s="75"/>
       <c r="Z16" s="75"/>
       <c r="AA16" s="75"/>
-      <c r="AB16" s="75" t="str">
+      <c r="AB16" s="75">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v/>
+        <v>8.7200000000000006</v>
       </c>
       <c r="AC16" s="5" t="str">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="AD16" s="5" t="str">
+        <v>400V 3Nph</v>
+      </c>
+      <c r="AD16" s="5">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="AE16" s="5" t="str">
+        <v>24</v>
+      </c>
+      <c r="AE16" s="5">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v/>
-      </c>
-      <c r="AF16" s="5" t="str">
+        <v>32</v>
+      </c>
+      <c r="AF16" s="5">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v/>
+        <v>12.7</v>
       </c>
       <c r="AG16" s="5" t="str">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="AH16" s="48" t="str">
+        <v>1,240 x 1,685 x 765</v>
+      </c>
+      <c r="AH16" s="48">
         <f>IF($W16="","",VLOOKUP($W16,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v/>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B17" s="104"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="58" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D17" s="58" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E17" s="13">
-        <v>3.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F17" s="13">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="G17" s="18">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="H17" s="68" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I17" s="69">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J17" s="70" t="str">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K17" s="70" t="str">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3350,39 +3333,39 @@
       </c>
       <c r="M17" s="70">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="N17" s="70">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="O17" s="71">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>266.67</v>
+        <v>150</v>
       </c>
       <c r="P17" s="72">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.151</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q17" s="70" t="str">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>35 - 39</v>
+        <v>25 - 30</v>
       </c>
       <c r="R17" s="70" t="str">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S17" s="70">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="T17" s="70" t="str">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>700 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U17" s="73">
         <f>IF($H17="","",VLOOKUP($H17,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>27</v>
+        <v>23.5</v>
       </c>
       <c r="V17" s="74"/>
       <c r="W17" s="75"/>
@@ -3399,32 +3382,32 @@
       <c r="AH17" s="9"/>
     </row>
     <row r="18" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B18" s="104"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="58" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D18" s="58" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E18" s="13">
-        <v>8.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F18" s="13">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="G18" s="18">
-        <v>429</v>
+        <v>318</v>
       </c>
       <c r="H18" s="68" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I18" s="69">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="J18" s="70" t="str">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K18" s="70" t="str">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3436,39 +3419,39 @@
       </c>
       <c r="M18" s="70">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>9.9</v>
+        <v>2.5</v>
       </c>
       <c r="N18" s="70">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="O18" s="71">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>533.33000000000004</v>
+        <v>150</v>
       </c>
       <c r="P18" s="72">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.215</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q18" s="70" t="str">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>39 - 43</v>
+        <v>25 - 30</v>
       </c>
       <c r="R18" s="70" t="str">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S18" s="70">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="T18" s="70" t="str">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,400 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U18" s="73">
         <f>IF($H18="","",VLOOKUP($H18,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>45</v>
+        <v>23.5</v>
       </c>
       <c r="V18" s="74"/>
       <c r="W18" s="75"/>
@@ -3485,32 +3468,32 @@
       <c r="AH18" s="9"/>
     </row>
     <row r="19" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B19" s="104"/>
+      <c r="B19" s="86"/>
       <c r="C19" s="58" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="D19" s="58" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="E19" s="13">
-        <v>6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F19" s="13">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="G19" s="18">
         <v>318</v>
       </c>
       <c r="H19" s="68" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="I19" s="69">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="J19" s="70" t="str">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K19" s="70" t="str">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -3522,39 +3505,39 @@
       </c>
       <c r="M19" s="70">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>6.2</v>
+        <v>2.5</v>
       </c>
       <c r="N19" s="70">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>1.9</v>
       </c>
       <c r="O19" s="71">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>325</v>
+        <v>150</v>
       </c>
       <c r="P19" s="72">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.13800000000000001</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q19" s="70" t="str">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>38 - 42</v>
+        <v>25 - 30</v>
       </c>
       <c r="R19" s="70" t="str">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S19" s="70">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="T19" s="70" t="str">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U19" s="73">
         <f>IF($H19="","",VLOOKUP($H19,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>23.5</v>
       </c>
       <c r="V19" s="74"/>
       <c r="W19" s="75"/>
@@ -3570,65 +3553,77 @@
       <c r="AG19" s="8"/>
       <c r="AH19" s="9"/>
     </row>
-    <row r="20" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="104"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="69" t="str">
+    <row r="20" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B20" s="86"/>
+      <c r="C20" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E20" s="13">
+        <v>5.6</v>
+      </c>
+      <c r="F20" s="13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G20" s="18">
+        <v>253</v>
+      </c>
+      <c r="H20" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="69">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="J20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M20" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M20" s="70">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N20" s="70" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="N20" s="70">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O20" s="71" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="O20" s="71">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P20" s="72" t="str">
+        <v>350</v>
+      </c>
+      <c r="P20" s="72">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>27 - 33</v>
       </c>
       <c r="R20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S20" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S20" s="70">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>1.6</v>
       </c>
       <c r="T20" s="70" t="str">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U20" s="73" t="str">
+        <v>1,000 x 245 x 800</v>
+      </c>
+      <c r="U20" s="73">
         <f>IF($H20="","",VLOOKUP($H20,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>35.5</v>
       </c>
       <c r="V20" s="74"/>
       <c r="W20" s="75"/>
@@ -3644,65 +3639,77 @@
       <c r="AG20" s="8"/>
       <c r="AH20" s="9"/>
     </row>
-    <row r="21" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="104"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="69" t="str">
+    <row r="21" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B21" s="86"/>
+      <c r="C21" s="58" t="s">
+        <v>198</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E21" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F21" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="G21" s="18">
+        <v>318</v>
+      </c>
+      <c r="H21" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="69">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="J21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M21" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M21" s="70">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N21" s="70" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="N21" s="70">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O21" s="71" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="O21" s="71">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P21" s="72" t="str">
+        <v>150</v>
+      </c>
+      <c r="P21" s="72">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>25 - 30</v>
       </c>
       <c r="R21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S21" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S21" s="70">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="T21" s="70" t="str">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U21" s="73" t="str">
+        <v>550 x 245 x 800</v>
+      </c>
+      <c r="U21" s="73">
         <f>IF($H21="","",VLOOKUP($H21,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>23.5</v>
       </c>
       <c r="V21" s="74"/>
       <c r="W21" s="75"/>
@@ -3718,65 +3725,77 @@
       <c r="AG21" s="8"/>
       <c r="AH21" s="9"/>
     </row>
-    <row r="22" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="104"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="69" t="str">
+    <row r="22" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B22" s="86"/>
+      <c r="C22" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E22" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F22" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="G22" s="18">
+        <v>318</v>
+      </c>
+      <c r="H22" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="69">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="J22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M22" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M22" s="70">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N22" s="70" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="N22" s="70">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O22" s="71" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="O22" s="71">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P22" s="72" t="str">
+        <v>150</v>
+      </c>
+      <c r="P22" s="72">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>25 - 30</v>
       </c>
       <c r="R22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S22" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S22" s="70">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="T22" s="70" t="str">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U22" s="73" t="str">
+        <v>550 x 245 x 800</v>
+      </c>
+      <c r="U22" s="73">
         <f>IF($H22="","",VLOOKUP($H22,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>23.5</v>
       </c>
       <c r="V22" s="74"/>
       <c r="W22" s="75"/>
@@ -3792,65 +3811,77 @@
       <c r="AG22" s="8"/>
       <c r="AH22" s="9"/>
     </row>
-    <row r="23" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="104"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="69" t="str">
+    <row r="23" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B23" s="86"/>
+      <c r="C23" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="G23" s="18">
+        <v>318</v>
+      </c>
+      <c r="H23" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="69">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="J23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M23" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M23" s="70">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N23" s="70" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="N23" s="70">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O23" s="71" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="O23" s="71">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P23" s="72" t="str">
+        <v>150</v>
+      </c>
+      <c r="P23" s="72">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>25 - 30</v>
       </c>
       <c r="R23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S23" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S23" s="70">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="T23" s="70" t="str">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U23" s="73" t="str">
+        <v>550 x 245 x 800</v>
+      </c>
+      <c r="U23" s="73">
         <f>IF($H23="","",VLOOKUP($H23,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>23.5</v>
       </c>
       <c r="V23" s="74"/>
       <c r="W23" s="75"/>
@@ -3866,65 +3897,77 @@
       <c r="AG23" s="8"/>
       <c r="AH23" s="9"/>
     </row>
-    <row r="24" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="104"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="69" t="str">
+    <row r="24" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B24" s="86"/>
+      <c r="C24" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D24" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E24" s="13">
+        <v>9</v>
+      </c>
+      <c r="F24" s="13">
+        <v>6.5</v>
+      </c>
+      <c r="G24" s="18">
+        <v>812</v>
+      </c>
+      <c r="H24" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="69">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="J24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M24" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M24" s="70">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N24" s="70" t="str">
+        <v>9.9</v>
+      </c>
+      <c r="N24" s="70">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O24" s="71" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="O24" s="71">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P24" s="72" t="str">
+        <v>533.33000000000004</v>
+      </c>
+      <c r="P24" s="72">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>31 - 36</v>
       </c>
       <c r="R24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S24" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S24" s="70">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="T24" s="70" t="str">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U24" s="73" t="str">
+        <v>1,400 x 245 x 800</v>
+      </c>
+      <c r="U24" s="73">
         <f>IF($H24="","",VLOOKUP($H24,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="V24" s="74"/>
       <c r="W24" s="75"/>
@@ -3940,65 +3983,77 @@
       <c r="AG24" s="8"/>
       <c r="AH24" s="9"/>
     </row>
-    <row r="25" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="105"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="69" t="str">
+    <row r="25" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B25" s="87"/>
+      <c r="C25" s="58" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="13">
+        <v>9</v>
+      </c>
+      <c r="F25" s="13">
+        <v>6.5</v>
+      </c>
+      <c r="G25" s="18">
+        <v>812</v>
+      </c>
+      <c r="H25" s="68" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="69">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="J25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M25" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M25" s="70">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N25" s="70" t="str">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="70">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O25" s="71" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="O25" s="71">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P25" s="72" t="str">
+        <v>533.33000000000004</v>
+      </c>
+      <c r="P25" s="72">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>31 - 36</v>
       </c>
       <c r="R25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S25" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S25" s="70">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="T25" s="70" t="str">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U25" s="73" t="str">
+        <v>1,400 x 245 x 800</v>
+      </c>
+      <c r="U25" s="73">
         <f>IF($H25="","",VLOOKUP($H25,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="V25" s="79"/>
       <c r="W25" s="78"/>
@@ -4020,39 +4075,39 @@
       <c r="D26" s="32"/>
       <c r="E26" s="33">
         <f>SUM(E11:E25)</f>
-        <v>41</v>
+        <v>74.90000000000002</v>
       </c>
       <c r="F26" s="33">
         <f>SUM(F11:F25)</f>
-        <v>31.499999999999996</v>
+        <v>54.500000000000007</v>
       </c>
       <c r="G26" s="56">
         <f>SUM(G11:G25)</f>
-        <v>2114</v>
+        <v>6218</v>
       </c>
       <c r="H26" s="55"/>
       <c r="I26" s="51">
         <f>SUM(I11:I25)</f>
-        <v>483</v>
+        <v>841</v>
       </c>
       <c r="J26" s="36"/>
       <c r="K26" s="36"/>
       <c r="L26" s="36"/>
       <c r="M26" s="37">
         <f>SUM(M11:M25)</f>
-        <v>47.7</v>
+        <v>83.300000000000011</v>
       </c>
       <c r="N26" s="37">
         <f>SUM(N11:N25)</f>
-        <v>40.1</v>
+        <v>62.899999999999991</v>
       </c>
       <c r="O26" s="38">
         <f>SUM(O11:O25)</f>
-        <v>2858.34</v>
+        <v>4499.9799999999996</v>
       </c>
       <c r="P26" s="39">
         <f>SUM(P11:P25)</f>
-        <v>1.3180000000000001</v>
+        <v>1.413</v>
       </c>
       <c r="Q26" s="36"/>
       <c r="R26" s="36"/>
@@ -4063,14 +4118,14 @@
       <c r="W26" s="43"/>
       <c r="X26" s="50">
         <f>X16+X15+X14+X12</f>
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="Y26" s="43"/>
       <c r="Z26" s="43"/>
       <c r="AA26" s="43"/>
       <c r="AB26" s="44">
         <f>SUM(AB11:AB25)</f>
-        <v>15.5</v>
+        <v>26.160000000000004</v>
       </c>
       <c r="AC26" s="43"/>
       <c r="AD26" s="43"/>
@@ -4080,69 +4135,69 @@
       <c r="AH26" s="45"/>
     </row>
     <row r="27" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="119"/>
-      <c r="C27" s="120"/>
-      <c r="D27" s="120"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="120"/>
-      <c r="H27" s="120"/>
-      <c r="I27" s="120"/>
-      <c r="J27" s="120"/>
-      <c r="K27" s="120"/>
-      <c r="L27" s="120"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="120"/>
-      <c r="P27" s="120"/>
-      <c r="Q27" s="120"/>
-      <c r="R27" s="120"/>
-      <c r="S27" s="120"/>
-      <c r="T27" s="120"/>
-      <c r="U27" s="120"/>
-      <c r="V27" s="120"/>
-      <c r="W27" s="120"/>
-      <c r="X27" s="120"/>
-      <c r="Y27" s="120"/>
-      <c r="Z27" s="120"/>
-      <c r="AA27" s="120"/>
-      <c r="AB27" s="120"/>
-      <c r="AC27" s="120"/>
-      <c r="AD27" s="120"/>
-      <c r="AE27" s="120"/>
-      <c r="AF27" s="120"/>
-      <c r="AG27" s="120"/>
-      <c r="AH27" s="121"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
+      <c r="L27" s="89"/>
+      <c r="M27" s="89"/>
+      <c r="N27" s="89"/>
+      <c r="O27" s="89"/>
+      <c r="P27" s="89"/>
+      <c r="Q27" s="89"/>
+      <c r="R27" s="89"/>
+      <c r="S27" s="89"/>
+      <c r="T27" s="89"/>
+      <c r="U27" s="89"/>
+      <c r="V27" s="89"/>
+      <c r="W27" s="89"/>
+      <c r="X27" s="89"/>
+      <c r="Y27" s="89"/>
+      <c r="Z27" s="89"/>
+      <c r="AA27" s="89"/>
+      <c r="AB27" s="89"/>
+      <c r="AC27" s="89"/>
+      <c r="AD27" s="89"/>
+      <c r="AE27" s="89"/>
+      <c r="AF27" s="89"/>
+      <c r="AG27" s="89"/>
+      <c r="AH27" s="90"/>
     </row>
     <row r="28" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B28" s="103" t="s">
-        <v>208</v>
+      <c r="B28" s="85" t="s">
+        <v>223</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="E28" s="16">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" s="16">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="G28" s="17">
-        <v>249</v>
+        <v>812</v>
       </c>
       <c r="H28" s="81" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="I28" s="82">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J28" s="61" t="str">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K28" s="61" t="str">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4154,39 +4209,39 @@
       </c>
       <c r="M28" s="61">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>6.2</v>
+        <v>9.9</v>
       </c>
       <c r="N28" s="61">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="O28" s="62">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>325</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P28" s="63">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.13800000000000001</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q28" s="61" t="str">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>38 - 42</v>
+        <v>31 - 36</v>
       </c>
       <c r="R28" s="61" t="str">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S28" s="61">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="T28" s="61" t="str">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U28" s="61">
         <f>IF($H28="","",VLOOKUP($H28,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="V28" s="65"/>
       <c r="W28" s="66"/>
@@ -4203,32 +4258,32 @@
       <c r="AH28" s="11"/>
     </row>
     <row r="29" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B29" s="104"/>
+      <c r="B29" s="86"/>
       <c r="C29" s="58" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E29" s="13">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="F29" s="13">
-        <v>10.4</v>
+        <v>6.5</v>
       </c>
       <c r="G29" s="18">
-        <v>765</v>
+        <v>812</v>
       </c>
       <c r="H29" s="83" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="I29" s="84">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="J29" s="70" t="str">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K29" s="70" t="str">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4240,35 +4295,35 @@
       </c>
       <c r="M29" s="70">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>14.2</v>
+        <v>9.9</v>
       </c>
       <c r="N29" s="70">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>10.9</v>
+        <v>7.5</v>
       </c>
       <c r="O29" s="71">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>766.67</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P29" s="72">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.40500000000000003</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q29" s="70" t="str">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>43 - 46</v>
+        <v>31 - 36</v>
       </c>
       <c r="R29" s="70" t="str">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S29" s="70">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T29" s="70" t="str">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,400 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U29" s="70">
         <f>IF($H29="","",VLOOKUP($H29,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
@@ -4322,32 +4377,32 @@
       </c>
     </row>
     <row r="30" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B30" s="104"/>
+      <c r="B30" s="86"/>
       <c r="C30" s="58" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="E30" s="13">
-        <v>4.5999999999999996</v>
+        <v>5.6</v>
       </c>
       <c r="F30" s="13">
-        <v>3.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G30" s="18">
-        <v>221</v>
+        <v>253</v>
       </c>
       <c r="H30" s="83" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="I30" s="84">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="J30" s="70" t="str">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K30" s="70" t="str">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4359,27 +4414,27 @@
       </c>
       <c r="M30" s="70">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>6.2</v>
       </c>
       <c r="N30" s="70">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O30" s="71">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="P30" s="72">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q30" s="70" t="str">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>27 - 33</v>
       </c>
       <c r="R30" s="70" t="str">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S30" s="70">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
@@ -4387,28 +4442,28 @@
       </c>
       <c r="T30" s="70" t="str">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U30" s="70">
         <f>IF($H30="","",VLOOKUP($H30,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="V30" s="74" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="W30" s="75" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="X30" s="76"/>
       <c r="Y30" s="75">
         <v>46</v>
       </c>
       <c r="Z30" s="75">
-        <v>43.9</v>
+        <v>49.2</v>
       </c>
       <c r="AA30" s="77">
         <f>IF(W31="","",I43/X43)</f>
-        <v>1.026</v>
+        <v>0.92500000000000004</v>
       </c>
       <c r="AB30" s="75"/>
       <c r="AC30" s="5"/>
@@ -4426,32 +4481,32 @@
       <c r="AL30" s="52"/>
     </row>
     <row r="31" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B31" s="104"/>
+      <c r="B31" s="86"/>
       <c r="C31" s="58" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="E31" s="13">
-        <v>14.5</v>
+        <v>7.1</v>
       </c>
       <c r="F31" s="13">
-        <v>11.7</v>
+        <v>5.2</v>
       </c>
       <c r="G31" s="18">
-        <v>804</v>
+        <v>350</v>
       </c>
       <c r="H31" s="83" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="I31" s="84">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="J31" s="70" t="str">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K31" s="70" t="str">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4463,23 +4518,23 @@
       </c>
       <c r="M31" s="70">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>17.100000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="N31" s="70">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>13.9</v>
+        <v>5.9</v>
       </c>
       <c r="O31" s="71">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>966.67</v>
+        <v>383.33</v>
       </c>
       <c r="P31" s="72">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.9</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q31" s="70" t="str">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>42 - 45</v>
+        <v>29 - 35</v>
       </c>
       <c r="R31" s="70" t="str">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
@@ -4487,32 +4542,32 @@
       </c>
       <c r="S31" s="70">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>1.9</v>
       </c>
       <c r="T31" s="70" t="str">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,190 x 440 x 1,090</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U31" s="70">
         <f>IF($H31="","",VLOOKUP($H31,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>110</v>
+        <v>36.5</v>
       </c>
       <c r="V31" s="74" t="s">
         <v>23</v>
       </c>
       <c r="W31" s="75" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="X31" s="76">
         <f>IF($W31="",0,VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y31" s="75"/>
       <c r="Z31" s="75"/>
       <c r="AA31" s="75"/>
       <c r="AB31" s="75">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="AC31" s="5" t="str">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -4520,62 +4575,62 @@
       </c>
       <c r="AD31" s="5">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>26.9</v>
-      </c>
-      <c r="AE31" s="5" t="str">
+        <v>31</v>
+      </c>
+      <c r="AE31" s="5">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF31" s="5" t="str">
+        <v>40</v>
+      </c>
+      <c r="AF31" s="5">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>19.3</v>
       </c>
       <c r="AG31" s="5" t="str">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>1,240 x 1,657 x 765</v>
+        <v>1,240 x 1,685 x 765</v>
       </c>
       <c r="AH31" s="48">
         <f>IF($W31="","",VLOOKUP($W31,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>220</v>
+        <v>283</v>
       </c>
       <c r="AJ31" s="52" t="s">
         <v>186</v>
       </c>
       <c r="AK31" s="54">
         <f>(I43/AK30)/25</f>
-        <v>18.654545454545453</v>
+        <v>20.18181818181818</v>
       </c>
       <c r="AL31" s="52" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="32" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B32" s="104"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="58" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="E32" s="13">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="F32" s="13">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="G32" s="18">
-        <v>246</v>
+        <v>812</v>
       </c>
       <c r="H32" s="83" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I32" s="84">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J32" s="70" t="str">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K32" s="70" t="str">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4587,45 +4642,45 @@
       </c>
       <c r="M32" s="70">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>9.9</v>
       </c>
       <c r="N32" s="70">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="O32" s="71">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P32" s="72">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q32" s="70" t="str">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>31 - 36</v>
       </c>
       <c r="R32" s="70" t="str">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S32" s="70">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="T32" s="70" t="str">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U32" s="70">
         <f>IF($H32="","",VLOOKUP($H32,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="V32" s="74" t="s">
         <v>41</v>
       </c>
       <c r="W32" s="75" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="X32" s="76">
         <f>IF($W32="",0,VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
@@ -4636,7 +4691,7 @@
       <c r="AA32" s="75"/>
       <c r="AB32" s="75">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="AC32" s="5" t="str">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -4644,52 +4699,52 @@
       </c>
       <c r="AD32" s="5">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>21.2</v>
-      </c>
-      <c r="AE32" s="5" t="str">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="AE32" s="5">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF32" s="5" t="str">
+        <v>20</v>
+      </c>
+      <c r="AF32" s="5">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>8</v>
       </c>
       <c r="AG32" s="5" t="str">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>930 x 1,657 x 765</v>
+        <v>930 x 1,685 x 765</v>
       </c>
       <c r="AH32" s="48">
         <f>IF($W32="","",VLOOKUP($W32,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>175</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B33" s="104"/>
+      <c r="B33" s="86"/>
       <c r="C33" s="58" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="E33" s="13">
-        <v>3.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F33" s="13">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G33" s="18">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H33" s="83" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="I33" s="84">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J33" s="70" t="str">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K33" s="70" t="str">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -4701,39 +4756,39 @@
       </c>
       <c r="M33" s="70">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N33" s="70">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="O33" s="71">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>266.67</v>
+        <v>158.33000000000001</v>
       </c>
       <c r="P33" s="72">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.151</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="Q33" s="70" t="str">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>35 - 39</v>
+        <v>26 - 26</v>
       </c>
       <c r="R33" s="70" t="str">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S33" s="70">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="T33" s="70" t="str">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>700 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U33" s="70">
         <f>IF($H33="","",VLOOKUP($H33,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="V33" s="74"/>
       <c r="W33" s="75"/>
@@ -4779,65 +4834,77 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="104"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="84" t="str">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B34" s="86"/>
+      <c r="C34" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" s="13">
+        <v>7.1</v>
+      </c>
+      <c r="F34" s="13">
+        <v>5.3</v>
+      </c>
+      <c r="G34" s="18">
+        <v>317</v>
+      </c>
+      <c r="H34" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="84">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>80</v>
       </c>
       <c r="J34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M34" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M34" s="70">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N34" s="70" t="str">
+        <v>7.9</v>
+      </c>
+      <c r="N34" s="70">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O34" s="71" t="str">
+        <v>5.9</v>
+      </c>
+      <c r="O34" s="71">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P34" s="72" t="str">
+        <v>383.33</v>
+      </c>
+      <c r="P34" s="72">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.13500000000000001</v>
       </c>
       <c r="Q34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>29 - 35</v>
       </c>
       <c r="R34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S34" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S34" s="70">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>1.9</v>
       </c>
       <c r="T34" s="70" t="str">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U34" s="70" t="str">
+        <v>1,000 x 245 x 800</v>
+      </c>
+      <c r="U34" s="70">
         <f>IF($H34="","",VLOOKUP($H34,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>36.5</v>
       </c>
       <c r="V34" s="74"/>
       <c r="W34" s="75"/>
@@ -4854,7 +4921,7 @@
       <c r="AH34" s="9"/>
     </row>
     <row r="35" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="104"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="58"/>
       <c r="D35" s="58"/>
       <c r="E35" s="13"/>
@@ -4928,7 +4995,7 @@
       <c r="AH35" s="9"/>
     </row>
     <row r="36" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="104"/>
+      <c r="B36" s="86"/>
       <c r="C36" s="58"/>
       <c r="D36" s="58"/>
       <c r="E36" s="13"/>
@@ -5002,7 +5069,7 @@
       <c r="AH36" s="9"/>
     </row>
     <row r="37" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="104"/>
+      <c r="B37" s="86"/>
       <c r="C37" s="58"/>
       <c r="D37" s="58"/>
       <c r="E37" s="13"/>
@@ -5076,7 +5143,7 @@
       <c r="AH37" s="9"/>
     </row>
     <row r="38" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="104"/>
+      <c r="B38" s="86"/>
       <c r="C38" s="58"/>
       <c r="D38" s="58"/>
       <c r="E38" s="13"/>
@@ -5150,7 +5217,7 @@
       <c r="AH38" s="9"/>
     </row>
     <row r="39" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="104"/>
+      <c r="B39" s="86"/>
       <c r="C39" s="58"/>
       <c r="D39" s="58"/>
       <c r="E39" s="13"/>
@@ -5224,7 +5291,7 @@
       <c r="AH39" s="9"/>
     </row>
     <row r="40" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="104"/>
+      <c r="B40" s="86"/>
       <c r="C40" s="58"/>
       <c r="D40" s="58"/>
       <c r="E40" s="13"/>
@@ -5298,7 +5365,7 @@
       <c r="AH40" s="9"/>
     </row>
     <row r="41" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="104"/>
+      <c r="B41" s="86"/>
       <c r="C41" s="58"/>
       <c r="D41" s="58"/>
       <c r="E41" s="13"/>
@@ -5372,7 +5439,7 @@
       <c r="AH41" s="9"/>
     </row>
     <row r="42" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="105"/>
+      <c r="B42" s="87"/>
       <c r="C42" s="58"/>
       <c r="D42" s="58"/>
       <c r="E42" s="13"/>
@@ -5451,39 +5518,39 @@
       <c r="D43" s="32"/>
       <c r="E43" s="33">
         <f>SUM(E28:E42)</f>
-        <v>44.300000000000004</v>
+        <v>49.000000000000007</v>
       </c>
       <c r="F43" s="33">
         <f>SUM(F28:F42)</f>
-        <v>35.4</v>
+        <v>36</v>
       </c>
       <c r="G43" s="34">
         <f>SUM(G28:G42)</f>
-        <v>2436</v>
+        <v>3486</v>
       </c>
       <c r="H43" s="35"/>
       <c r="I43" s="51">
         <f>SUM(I28:I42)</f>
-        <v>513</v>
+        <v>555</v>
       </c>
       <c r="J43" s="36"/>
       <c r="K43" s="36"/>
       <c r="L43" s="36"/>
       <c r="M43" s="37">
         <f>SUM(M28:M42)</f>
-        <v>51.3</v>
+        <v>54.9</v>
       </c>
       <c r="N43" s="37">
         <f>SUM(N28:N42)</f>
-        <v>41.800000000000004</v>
+        <v>41.4</v>
       </c>
       <c r="O43" s="38">
         <f>SUM(O28:O42)</f>
-        <v>2925.01</v>
+        <v>2874.98</v>
       </c>
       <c r="P43" s="39">
         <f>SUM(P28:P42)</f>
-        <v>1.8500000000000003</v>
+        <v>0.93499999999999994</v>
       </c>
       <c r="Q43" s="36"/>
       <c r="R43" s="36"/>
@@ -5494,14 +5561,14 @@
       <c r="W43" s="43"/>
       <c r="X43" s="50">
         <f>X33+X32+X31+X29</f>
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="Y43" s="43"/>
       <c r="Z43" s="43"/>
       <c r="AA43" s="43"/>
       <c r="AB43" s="44">
         <f>SUM(AB28:AB42)</f>
-        <v>16.899999999999999</v>
+        <v>18.66</v>
       </c>
       <c r="AC43" s="43"/>
       <c r="AD43" s="43"/>
@@ -5511,69 +5578,69 @@
       <c r="AH43" s="45"/>
     </row>
     <row r="44" spans="2:38" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="119"/>
-      <c r="C44" s="120"/>
-      <c r="D44" s="120"/>
-      <c r="E44" s="120"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="120"/>
-      <c r="H44" s="120"/>
-      <c r="I44" s="120"/>
-      <c r="J44" s="120"/>
-      <c r="K44" s="120"/>
-      <c r="L44" s="120"/>
-      <c r="M44" s="120"/>
-      <c r="N44" s="120"/>
-      <c r="O44" s="120"/>
-      <c r="P44" s="120"/>
-      <c r="Q44" s="120"/>
-      <c r="R44" s="120"/>
-      <c r="S44" s="120"/>
-      <c r="T44" s="120"/>
-      <c r="U44" s="120"/>
-      <c r="V44" s="120"/>
-      <c r="W44" s="120"/>
-      <c r="X44" s="120"/>
-      <c r="Y44" s="120"/>
-      <c r="Z44" s="120"/>
-      <c r="AA44" s="120"/>
-      <c r="AB44" s="120"/>
-      <c r="AC44" s="120"/>
-      <c r="AD44" s="120"/>
-      <c r="AE44" s="120"/>
-      <c r="AF44" s="120"/>
-      <c r="AG44" s="120"/>
-      <c r="AH44" s="121"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="89"/>
+      <c r="D44" s="89"/>
+      <c r="E44" s="89"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="89"/>
+      <c r="J44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="89"/>
+      <c r="M44" s="89"/>
+      <c r="N44" s="89"/>
+      <c r="O44" s="89"/>
+      <c r="P44" s="89"/>
+      <c r="Q44" s="89"/>
+      <c r="R44" s="89"/>
+      <c r="S44" s="89"/>
+      <c r="T44" s="89"/>
+      <c r="U44" s="89"/>
+      <c r="V44" s="89"/>
+      <c r="W44" s="89"/>
+      <c r="X44" s="89"/>
+      <c r="Y44" s="89"/>
+      <c r="Z44" s="89"/>
+      <c r="AA44" s="89"/>
+      <c r="AB44" s="89"/>
+      <c r="AC44" s="89"/>
+      <c r="AD44" s="89"/>
+      <c r="AE44" s="89"/>
+      <c r="AF44" s="89"/>
+      <c r="AG44" s="89"/>
+      <c r="AH44" s="90"/>
     </row>
     <row r="45" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B45" s="103" t="s">
-        <v>222</v>
+      <c r="B45" s="85" t="s">
+        <v>225</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E45" s="16">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="F45" s="16">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G45" s="17">
-        <v>630</v>
+        <v>812</v>
       </c>
       <c r="H45" s="81" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="I45" s="82">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J45" s="61" t="str">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K45" s="61" t="str">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -5585,39 +5652,39 @@
       </c>
       <c r="M45" s="61">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
       <c r="N45" s="61">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="O45" s="62">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>650</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P45" s="63">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.28399999999999997</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q45" s="61" t="str">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>40 - 44</v>
+        <v>31 - 36</v>
       </c>
       <c r="R45" s="61" t="str">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S45" s="61">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T45" s="61" t="str">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,400 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U45" s="61">
         <f>IF($H45="","",VLOOKUP($H45,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V45" s="65"/>
       <c r="W45" s="66"/>
@@ -5634,32 +5701,32 @@
       <c r="AH45" s="11"/>
     </row>
     <row r="46" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B46" s="104"/>
+      <c r="B46" s="86"/>
       <c r="C46" s="58" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D46" s="58" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E46" s="13">
-        <v>4.5999999999999996</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F46" s="13">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="G46" s="18">
-        <v>243</v>
+        <v>318</v>
       </c>
       <c r="H46" s="83" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="I46" s="84">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="J46" s="70" t="str">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K46" s="70" t="str">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -5671,39 +5738,39 @@
       </c>
       <c r="M46" s="70">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>4.9000000000000004</v>
+        <v>2.5</v>
       </c>
       <c r="N46" s="70">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="O46" s="71">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="P46" s="72">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.128</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q46" s="70" t="str">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>37 - 41</v>
+        <v>25 - 30</v>
       </c>
       <c r="R46" s="70" t="str">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S46" s="70">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="T46" s="70" t="str">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>550 x 245 x 800</v>
       </c>
       <c r="U46" s="70">
         <f>IF($H46="","",VLOOKUP($H46,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>23.5</v>
       </c>
       <c r="V46" s="74"/>
       <c r="W46" s="75"/>
@@ -5753,24 +5820,24 @@
       </c>
     </row>
     <row r="47" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B47" s="104"/>
+      <c r="B47" s="86"/>
       <c r="C47" s="58" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="D47" s="58" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="E47" s="13">
         <v>5.6</v>
       </c>
       <c r="F47" s="13">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G47" s="18">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H47" s="83" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="I47" s="84">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
@@ -5778,7 +5845,7 @@
       </c>
       <c r="J47" s="70" t="str">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K47" s="70" t="str">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -5794,52 +5861,52 @@
       </c>
       <c r="N47" s="70">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>4.7</v>
       </c>
       <c r="O47" s="71">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="P47" s="72">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.13800000000000001</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q47" s="70" t="str">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>38 - 42</v>
+        <v>27 - 33</v>
       </c>
       <c r="R47" s="70" t="str">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S47" s="70">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="T47" s="70" t="str">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,000 x 245 x 800</v>
       </c>
       <c r="U47" s="70">
         <f>IF($H47="","",VLOOKUP($H47,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="V47" s="74" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="W47" s="75" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="X47" s="76"/>
       <c r="Y47" s="75">
         <v>46</v>
       </c>
       <c r="Z47" s="75">
-        <v>38.1</v>
+        <v>59.9</v>
       </c>
       <c r="AA47" s="77">
         <f>IF(W48="","",I60/X60)</f>
-        <v>0.94666666666666666</v>
+        <v>0.90133333333333332</v>
       </c>
       <c r="AB47" s="5"/>
       <c r="AC47" s="5"/>
@@ -5857,32 +5924,32 @@
       <c r="AL47" s="52"/>
     </row>
     <row r="48" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B48" s="104"/>
+      <c r="B48" s="86"/>
       <c r="C48" s="58" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E48" s="13">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="F48" s="13">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G48" s="18">
-        <v>498</v>
+        <v>812</v>
       </c>
       <c r="H48" s="83" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="I48" s="84">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="J48" s="70" t="str">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K48" s="70" t="str">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -5894,56 +5961,56 @@
       </c>
       <c r="M48" s="70">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>12.4</v>
+        <v>9.9</v>
       </c>
       <c r="N48" s="70">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>9.6</v>
+        <v>7.5</v>
       </c>
       <c r="O48" s="71">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>650</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P48" s="72">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.28399999999999997</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q48" s="70" t="str">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>40 - 44</v>
+        <v>31 - 36</v>
       </c>
       <c r="R48" s="70" t="str">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S48" s="70">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="T48" s="70" t="str">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,400 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U48" s="70">
         <f>IF($H48="","",VLOOKUP($H48,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V48" s="74" t="s">
         <v>23</v>
       </c>
       <c r="W48" s="75" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="X48" s="76">
         <f>IF($W48="",0,VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y48" s="75"/>
       <c r="Z48" s="75"/>
       <c r="AA48" s="75"/>
       <c r="AB48" s="5">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="AC48" s="5" t="str">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -5951,62 +6018,62 @@
       </c>
       <c r="AD48" s="5">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>26.9</v>
-      </c>
-      <c r="AE48" s="5" t="str">
+        <v>31</v>
+      </c>
+      <c r="AE48" s="5">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF48" s="5" t="str">
+        <v>40</v>
+      </c>
+      <c r="AF48" s="5">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>19.3</v>
       </c>
       <c r="AG48" s="5" t="str">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>1,240 x 1,657 x 765</v>
+        <v>1,240 x 1,685 x 765</v>
       </c>
       <c r="AH48" s="48">
         <f>IF($W48="","",VLOOKUP($W48,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>220</v>
+        <v>283</v>
       </c>
       <c r="AJ48" s="52" t="s">
         <v>186</v>
       </c>
       <c r="AK48" s="54">
         <f>(I60/AK47)/25</f>
-        <v>15.49090909090909</v>
+        <v>24.581818181818178</v>
       </c>
       <c r="AL48" s="52" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="49" spans="2:38" x14ac:dyDescent="0.25">
-      <c r="B49" s="104"/>
+      <c r="B49" s="86"/>
       <c r="C49" s="58" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="D49" s="58" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="E49" s="13">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="F49" s="13">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="G49" s="18">
-        <v>266</v>
+        <v>812</v>
       </c>
       <c r="H49" s="83" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="I49" s="84">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="J49" s="70" t="str">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v>India</v>
+        <v>Czech Republic</v>
       </c>
       <c r="K49" s="70" t="str">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
@@ -6018,56 +6085,56 @@
       </c>
       <c r="M49" s="70">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v>6.2</v>
+        <v>9.9</v>
       </c>
       <c r="N49" s="70">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>7.5</v>
       </c>
       <c r="O49" s="71">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v>325</v>
+        <v>533.33000000000004</v>
       </c>
       <c r="P49" s="72">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v>0.13800000000000001</v>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q49" s="70" t="str">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v>38 - 42</v>
+        <v>31 - 36</v>
       </c>
       <c r="R49" s="70" t="str">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v>230V 1ph</v>
+        <v>220V 1ph</v>
       </c>
       <c r="S49" s="70">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="T49" s="70" t="str">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v>1,000 x 300 x 700</v>
+        <v>1,400 x 245 x 800</v>
       </c>
       <c r="U49" s="70">
         <f>IF($H49="","",VLOOKUP($H49,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="V49" s="74" t="s">
         <v>41</v>
       </c>
       <c r="W49" s="75" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="X49" s="76">
         <f>IF($W49="",0,VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="Y49" s="75"/>
       <c r="Z49" s="75"/>
       <c r="AA49" s="75"/>
       <c r="AB49" s="5">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
-        <v>5.0999999999999996</v>
+        <v>10</v>
       </c>
       <c r="AC49" s="5" t="str">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,5,FALSE))</f>
@@ -6075,84 +6142,96 @@
       </c>
       <c r="AD49" s="5">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,6,FALSE))</f>
-        <v>16.100000000000001</v>
-      </c>
-      <c r="AE49" s="5" t="str">
+        <v>27</v>
+      </c>
+      <c r="AE49" s="5">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,7,FALSE))</f>
-        <v>-</v>
-      </c>
-      <c r="AF49" s="5" t="str">
+        <v>32</v>
+      </c>
+      <c r="AF49" s="5">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,8,FALSE))</f>
-        <v>-</v>
+        <v>15.8</v>
       </c>
       <c r="AG49" s="5" t="str">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,9,FALSE))</f>
-        <v>930 x 1,657 x 765</v>
+        <v>1,240 x 1,685 x 765</v>
       </c>
       <c r="AH49" s="48">
         <f>IF($W49="","",VLOOKUP($W49,'Outdoor Data'!$B$6:$L$16,10,FALSE))</f>
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="104"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="18"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="84" t="str">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="50" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B50" s="86"/>
+      <c r="C50" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="D50" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="13">
+        <v>9</v>
+      </c>
+      <c r="F50" s="13">
+        <v>6.5</v>
+      </c>
+      <c r="G50" s="18">
+        <v>812</v>
+      </c>
+      <c r="H50" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="I50" s="84">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="J50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M50" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M50" s="70">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N50" s="70" t="str">
+        <v>9.9</v>
+      </c>
+      <c r="N50" s="70">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O50" s="71" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="O50" s="71">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P50" s="72" t="str">
+        <v>533.33000000000004</v>
+      </c>
+      <c r="P50" s="72">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>31 - 36</v>
       </c>
       <c r="R50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S50" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S50" s="70">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="T50" s="70" t="str">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U50" s="70" t="str">
+        <v>1,400 x 245 x 800</v>
+      </c>
+      <c r="U50" s="70">
         <f>IF($H50="","",VLOOKUP($H50,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="V50" s="74"/>
       <c r="W50" s="75"/>
@@ -6160,14 +6239,8 @@
         <f>IF($W50="",0,VLOOKUP($W50,'Outdoor Data'!$B$6:$L$16,11,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="Y50" s="75" t="str">
-        <f>IF($W50="","",VLOOKUP($W50,'Outdoor Data'!$B$6:$L$16,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="Z50" s="75" t="str">
-        <f>IF($W50="","",VLOOKUP($W50,'Outdoor Data'!$B$6:$L$16,3,FALSE))</f>
-        <v/>
-      </c>
+      <c r="Y50" s="75"/>
+      <c r="Z50" s="75"/>
       <c r="AA50" s="75"/>
       <c r="AB50" s="5" t="str">
         <f>IF($W50="","",VLOOKUP($W50,'Outdoor Data'!$B$6:$L$16,4,FALSE))</f>
@@ -6198,65 +6271,77 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="104"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="84" t="str">
+    <row r="51" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B51" s="86"/>
+      <c r="C51" s="58" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" s="58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E51" s="13">
+        <v>5.6</v>
+      </c>
+      <c r="F51" s="13">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G51" s="18">
+        <v>253</v>
+      </c>
+      <c r="H51" s="83" t="s">
+        <v>43</v>
+      </c>
+      <c r="I51" s="84">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>63</v>
       </c>
       <c r="J51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M51" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M51" s="70">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N51" s="70" t="str">
+        <v>6.2</v>
+      </c>
+      <c r="N51" s="70">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O51" s="71" t="str">
+        <v>4.7</v>
+      </c>
+      <c r="O51" s="71">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P51" s="72" t="str">
+        <v>350</v>
+      </c>
+      <c r="P51" s="72">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.10100000000000001</v>
       </c>
       <c r="Q51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>27 - 33</v>
       </c>
       <c r="R51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S51" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S51" s="70">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>1.6</v>
       </c>
       <c r="T51" s="70" t="str">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U51" s="70" t="str">
+        <v>1,000 x 245 x 800</v>
+      </c>
+      <c r="U51" s="70">
         <f>IF($H51="","",VLOOKUP($H51,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>35.5</v>
       </c>
       <c r="V51" s="74"/>
       <c r="W51" s="75"/>
@@ -6272,65 +6357,77 @@
       <c r="AG51" s="8"/>
       <c r="AH51" s="9"/>
     </row>
-    <row r="52" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="104"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="18"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="84" t="str">
+    <row r="52" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B52" s="86"/>
+      <c r="C52" s="58" t="s">
+        <v>217</v>
+      </c>
+      <c r="D52" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E52" s="13">
+        <v>9</v>
+      </c>
+      <c r="F52" s="13">
+        <v>6.5</v>
+      </c>
+      <c r="G52" s="18">
+        <v>912</v>
+      </c>
+      <c r="H52" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="I52" s="84">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>100</v>
       </c>
       <c r="J52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M52" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M52" s="70">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N52" s="70" t="str">
+        <v>9.9</v>
+      </c>
+      <c r="N52" s="70">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O52" s="71" t="str">
+        <v>7.5</v>
+      </c>
+      <c r="O52" s="71">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P52" s="72" t="str">
+        <v>533.33000000000004</v>
+      </c>
+      <c r="P52" s="72">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>0.17299999999999999</v>
       </c>
       <c r="Q52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>31 - 36</v>
       </c>
       <c r="R52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S52" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S52" s="70">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>2.4</v>
       </c>
       <c r="T52" s="70" t="str">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U52" s="70" t="str">
+        <v>1,400 x 245 x 800</v>
+      </c>
+      <c r="U52" s="70">
         <f>IF($H52="","",VLOOKUP($H52,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="V52" s="74"/>
       <c r="W52" s="75"/>
@@ -6346,65 +6443,77 @@
       <c r="AG52" s="8"/>
       <c r="AH52" s="9"/>
     </row>
-    <row r="53" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="104"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="18"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="84" t="str">
+    <row r="53" spans="2:38" x14ac:dyDescent="0.25">
+      <c r="B53" s="86"/>
+      <c r="C53" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D53" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E53" s="13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F53" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="G53" s="18">
+        <v>318</v>
+      </c>
+      <c r="H53" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="I53" s="84">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,13,FALSE))</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="J53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,14,FALSE))</f>
-        <v/>
+        <v>Czech Republic</v>
       </c>
       <c r="K53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,2,FALSE))</f>
-        <v/>
+        <v>Ducted</v>
       </c>
       <c r="L53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,3,FALSE))</f>
-        <v/>
-      </c>
-      <c r="M53" s="70" t="str">
+        <v>46 - 24.4/17.2</v>
+      </c>
+      <c r="M53" s="70">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,4,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N53" s="70" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="N53" s="70">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,5,FALSE))</f>
-        <v/>
-      </c>
-      <c r="O53" s="71" t="str">
+        <v>1.9</v>
+      </c>
+      <c r="O53" s="71">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,6,FALSE))</f>
-        <v/>
-      </c>
-      <c r="P53" s="72" t="str">
+        <v>150</v>
+      </c>
+      <c r="P53" s="72">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,7,FALSE))</f>
-        <v/>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="Q53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,8,FALSE))</f>
-        <v/>
+        <v>25 - 30</v>
       </c>
       <c r="R53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,9,FALSE))</f>
-        <v/>
-      </c>
-      <c r="S53" s="70" t="str">
+        <v>220V 1ph</v>
+      </c>
+      <c r="S53" s="70">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,10,FALSE))</f>
-        <v/>
+        <v>0.8</v>
       </c>
       <c r="T53" s="70" t="str">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,11,FALSE))</f>
-        <v/>
-      </c>
-      <c r="U53" s="70" t="str">
+        <v>550 x 245 x 800</v>
+      </c>
+      <c r="U53" s="70">
         <f>IF($H53="","",VLOOKUP($H53,'Indoor Data'!$B$6:$O$57,12,FALSE))</f>
-        <v/>
+        <v>23.5</v>
       </c>
       <c r="V53" s="74"/>
       <c r="W53" s="75"/>
@@ -6421,7 +6530,7 @@
       <c r="AH53" s="9"/>
     </row>
     <row r="54" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="104"/>
+      <c r="B54" s="86"/>
       <c r="C54" s="58"/>
       <c r="D54" s="58"/>
       <c r="E54" s="13"/>
@@ -6495,7 +6604,7 @@
       <c r="AH54" s="9"/>
     </row>
     <row r="55" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="104"/>
+      <c r="B55" s="86"/>
       <c r="C55" s="58"/>
       <c r="D55" s="58"/>
       <c r="E55" s="13"/>
@@ -6569,7 +6678,7 @@
       <c r="AH55" s="9"/>
     </row>
     <row r="56" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="104"/>
+      <c r="B56" s="86"/>
       <c r="C56" s="58"/>
       <c r="D56" s="58"/>
       <c r="E56" s="13"/>
@@ -6643,7 +6752,7 @@
       <c r="AH56" s="9"/>
     </row>
     <row r="57" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="104"/>
+      <c r="B57" s="86"/>
       <c r="C57" s="58"/>
       <c r="D57" s="58"/>
       <c r="E57" s="13"/>
@@ -6717,7 +6826,7 @@
       <c r="AH57" s="9"/>
     </row>
     <row r="58" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="104"/>
+      <c r="B58" s="86"/>
       <c r="C58" s="58"/>
       <c r="D58" s="58"/>
       <c r="E58" s="13"/>
@@ -6791,7 +6900,7 @@
       <c r="AH58" s="9"/>
     </row>
     <row r="59" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="105"/>
+      <c r="B59" s="87"/>
       <c r="C59" s="58"/>
       <c r="D59" s="58"/>
       <c r="E59" s="13"/>
@@ -6870,39 +6979,39 @@
       <c r="D60" s="32"/>
       <c r="E60" s="33">
         <f>SUM(E45:E59)</f>
-        <v>36.800000000000004</v>
+        <v>60.6</v>
       </c>
       <c r="F60" s="33">
         <f>SUM(F45:F59)</f>
-        <v>29.2</v>
+        <v>43.9</v>
       </c>
       <c r="G60" s="34">
         <f>SUM(G45:G59)</f>
-        <v>1893</v>
+        <v>5302</v>
       </c>
       <c r="H60" s="35"/>
       <c r="I60" s="51">
         <f>SUM(I45:I59)</f>
-        <v>426</v>
+        <v>676</v>
       </c>
       <c r="J60" s="36"/>
       <c r="K60" s="36"/>
       <c r="L60" s="36"/>
       <c r="M60" s="37">
         <f>SUM(M45:M59)</f>
-        <v>42.1</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="N60" s="37">
         <f>SUM(N45:N59)</f>
-        <v>33.6</v>
+        <v>50.7</v>
       </c>
       <c r="O60" s="38">
         <f>SUM(O45:O59)</f>
-        <v>2250</v>
+        <v>3666.6499999999996</v>
       </c>
       <c r="P60" s="39">
         <f>SUM(P45:P59)</f>
-        <v>0.97200000000000009</v>
+        <v>1.149</v>
       </c>
       <c r="Q60" s="36"/>
       <c r="R60" s="36"/>
@@ -6913,14 +7022,14 @@
       <c r="W60" s="43"/>
       <c r="X60" s="50">
         <f>X50+X49+X48+X46</f>
-        <v>450</v>
+        <v>750</v>
       </c>
       <c r="Y60" s="43"/>
       <c r="Z60" s="43"/>
       <c r="AA60" s="43"/>
       <c r="AB60" s="44">
         <f>SUM(AB45:AB59)</f>
-        <v>15.5</v>
+        <v>22.1</v>
       </c>
       <c r="AC60" s="43"/>
       <c r="AD60" s="43"/>
@@ -6930,42 +7039,42 @@
       <c r="AH60" s="45"/>
     </row>
     <row r="61" spans="2:38" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="119"/>
-      <c r="C61" s="120"/>
-      <c r="D61" s="120"/>
-      <c r="E61" s="120"/>
-      <c r="F61" s="120"/>
-      <c r="G61" s="120"/>
-      <c r="H61" s="120"/>
-      <c r="I61" s="120"/>
-      <c r="J61" s="120"/>
-      <c r="K61" s="120"/>
-      <c r="L61" s="120"/>
-      <c r="M61" s="120"/>
-      <c r="N61" s="120"/>
-      <c r="O61" s="120"/>
-      <c r="P61" s="120"/>
-      <c r="Q61" s="120"/>
-      <c r="R61" s="120"/>
-      <c r="S61" s="120"/>
-      <c r="T61" s="120"/>
-      <c r="U61" s="120"/>
-      <c r="V61" s="120"/>
-      <c r="W61" s="120"/>
-      <c r="X61" s="120"/>
-      <c r="Y61" s="120"/>
-      <c r="Z61" s="120"/>
-      <c r="AA61" s="120"/>
-      <c r="AB61" s="120"/>
-      <c r="AC61" s="120"/>
-      <c r="AD61" s="120"/>
-      <c r="AE61" s="120"/>
-      <c r="AF61" s="120"/>
-      <c r="AG61" s="120"/>
-      <c r="AH61" s="121"/>
+      <c r="B61" s="88"/>
+      <c r="C61" s="89"/>
+      <c r="D61" s="89"/>
+      <c r="E61" s="89"/>
+      <c r="F61" s="89"/>
+      <c r="G61" s="89"/>
+      <c r="H61" s="89"/>
+      <c r="I61" s="89"/>
+      <c r="J61" s="89"/>
+      <c r="K61" s="89"/>
+      <c r="L61" s="89"/>
+      <c r="M61" s="89"/>
+      <c r="N61" s="89"/>
+      <c r="O61" s="89"/>
+      <c r="P61" s="89"/>
+      <c r="Q61" s="89"/>
+      <c r="R61" s="89"/>
+      <c r="S61" s="89"/>
+      <c r="T61" s="89"/>
+      <c r="U61" s="89"/>
+      <c r="V61" s="89"/>
+      <c r="W61" s="89"/>
+      <c r="X61" s="89"/>
+      <c r="Y61" s="89"/>
+      <c r="Z61" s="89"/>
+      <c r="AA61" s="89"/>
+      <c r="AB61" s="89"/>
+      <c r="AC61" s="89"/>
+      <c r="AD61" s="89"/>
+      <c r="AE61" s="89"/>
+      <c r="AF61" s="89"/>
+      <c r="AG61" s="89"/>
+      <c r="AH61" s="90"/>
     </row>
     <row r="62" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="103" t="s">
+      <c r="B62" s="85" t="s">
         <v>184</v>
       </c>
       <c r="C62" s="57"/>
@@ -7041,7 +7150,7 @@
       <c r="AH62" s="11"/>
     </row>
     <row r="63" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="104"/>
+      <c r="B63" s="86"/>
       <c r="C63" s="58"/>
       <c r="D63" s="58"/>
       <c r="E63" s="13"/>
@@ -7150,7 +7259,7 @@
       </c>
     </row>
     <row r="64" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="104"/>
+      <c r="B64" s="86"/>
       <c r="C64" s="58"/>
       <c r="D64" s="58"/>
       <c r="E64" s="13"/>
@@ -7236,7 +7345,7 @@
       <c r="AL64" s="52"/>
     </row>
     <row r="65" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="104"/>
+      <c r="B65" s="86"/>
       <c r="C65" s="58"/>
       <c r="D65" s="58"/>
       <c r="E65" s="13"/>
@@ -7352,7 +7461,7 @@
       </c>
     </row>
     <row r="66" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="104"/>
+      <c r="B66" s="86"/>
       <c r="C66" s="58"/>
       <c r="D66" s="58"/>
       <c r="E66" s="13"/>
@@ -7458,7 +7567,7 @@
       </c>
     </row>
     <row r="67" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="104"/>
+      <c r="B67" s="86"/>
       <c r="C67" s="58"/>
       <c r="D67" s="58"/>
       <c r="E67" s="13"/>
@@ -7564,7 +7673,7 @@
       </c>
     </row>
     <row r="68" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="104"/>
+      <c r="B68" s="86"/>
       <c r="C68" s="58"/>
       <c r="D68" s="58"/>
       <c r="E68" s="13"/>
@@ -7638,7 +7747,7 @@
       <c r="AH68" s="9"/>
     </row>
     <row r="69" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="104"/>
+      <c r="B69" s="86"/>
       <c r="C69" s="58"/>
       <c r="D69" s="58"/>
       <c r="E69" s="13"/>
@@ -7712,7 +7821,7 @@
       <c r="AH69" s="9"/>
     </row>
     <row r="70" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="104"/>
+      <c r="B70" s="86"/>
       <c r="C70" s="58"/>
       <c r="D70" s="58"/>
       <c r="E70" s="13"/>
@@ -7786,7 +7895,7 @@
       <c r="AH70" s="9"/>
     </row>
     <row r="71" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="104"/>
+      <c r="B71" s="86"/>
       <c r="C71" s="58"/>
       <c r="D71" s="58"/>
       <c r="E71" s="13"/>
@@ -7860,7 +7969,7 @@
       <c r="AH71" s="9"/>
     </row>
     <row r="72" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="104"/>
+      <c r="B72" s="86"/>
       <c r="C72" s="58"/>
       <c r="D72" s="58"/>
       <c r="E72" s="13"/>
@@ -7934,7 +8043,7 @@
       <c r="AH72" s="9"/>
     </row>
     <row r="73" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="104"/>
+      <c r="B73" s="86"/>
       <c r="C73" s="58"/>
       <c r="D73" s="58"/>
       <c r="E73" s="13"/>
@@ -8008,7 +8117,7 @@
       <c r="AH73" s="9"/>
     </row>
     <row r="74" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="104"/>
+      <c r="B74" s="86"/>
       <c r="C74" s="58"/>
       <c r="D74" s="58"/>
       <c r="E74" s="13"/>
@@ -8082,7 +8191,7 @@
       <c r="AH74" s="9"/>
     </row>
     <row r="75" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="104"/>
+      <c r="B75" s="86"/>
       <c r="C75" s="58"/>
       <c r="D75" s="58"/>
       <c r="E75" s="13"/>
@@ -8156,7 +8265,7 @@
       <c r="AH75" s="9"/>
     </row>
     <row r="76" spans="2:38" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="105"/>
+      <c r="B76" s="87"/>
       <c r="C76" s="58"/>
       <c r="D76" s="58"/>
       <c r="E76" s="13"/>
@@ -8296,32 +8405,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B45:B59"/>
-    <mergeCell ref="B61:AH61"/>
-    <mergeCell ref="B62:B76"/>
-    <mergeCell ref="B27:AH27"/>
-    <mergeCell ref="B28:B42"/>
-    <mergeCell ref="B44:AH44"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="AD9:AD10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="AE9:AE10"/>
-    <mergeCell ref="B11:B25"/>
-    <mergeCell ref="K8:K10"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
     <mergeCell ref="AG9:AG10"/>
     <mergeCell ref="X8:X10"/>
     <mergeCell ref="B6:AH6"/>
@@ -8338,6 +8421,32 @@
     <mergeCell ref="AC8:AC10"/>
     <mergeCell ref="AF9:AF10"/>
     <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="B11:B25"/>
+    <mergeCell ref="K8:K10"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="B45:B59"/>
+    <mergeCell ref="B61:AH61"/>
+    <mergeCell ref="B62:B76"/>
+    <mergeCell ref="B27:AH27"/>
+    <mergeCell ref="B28:B42"/>
+    <mergeCell ref="B44:AH44"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8356,7 +8465,7 @@
           <x14:formula1>
             <xm:f>'Outdoor Data'!$B$6:$B$16</xm:f>
           </x14:formula1>
-          <xm:sqref>W12 W31:W33 W29 W65:W67 W46 W14:W16 W63 W48:W50</xm:sqref>
+          <xm:sqref>W12 W31:W33 W29 W65:W67 W46 W48:W50 W63 W14:W16</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -10814,11 +10923,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="O3:O5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="J3:J5"/>
@@ -10827,6 +10931,11 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="O3:O5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11339,17 +11448,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
     <mergeCell ref="L3:L5"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="F3:F5"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
